--- a/docs/inspire-change-2025-grants.xlsx
+++ b/docs/inspire-change-2025-grants.xlsx
@@ -108,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -128,7 +128,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -225,38 +224,38 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>ein
-Nine digits. 74-1234567 or 741234567 both fine. TEXT COLUMN.</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
         <t>program_slug
 Always inspire-change</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <t>awarded_amount
 25000 or $25,000 or 25000.00</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <t>awarded_date
 YYYY-MM-DD. TEXT COLUMN.</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>grantee_contact_name
-Person who ran the grant.</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>grantee_contact_email
 Where their sign-in link goes. Must be reachable today.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>ein
+Nine digits, from their W-9. BLANK IS FINE. TEXT COLUMN.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>grantee_contact_name
+Person who ran the grant. Blank is fine for a shared mailbox.</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
@@ -612,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -636,36 +635,36 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>The two things that will break the import</t>
+          <t>The only column you have to fill in</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1. DATES. Excel rewrites 2023-04-12 as 04/12/2023 when it saves. Every date column in the Awards sheet is already formatted as Text so it will not do that. Do not reformat those columns, and type dates as YYYY-MM-DD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2. EINs. Excel strips a leading zero, so 012345678 becomes 12345678 and the import refuses it. The ein column is also formatted as Text. Dashes are fine either way.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>How to save it</t>
+          <t>awarded_date. One date for the whole year is fine. Everything else is either already filled in or genuinely optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>EIN and contact name are optional, and here is what a blank costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>A blank EIN means the organization is not matched on one. If that nonprofit later applies and gives their EIN, they arrive as a second organization for an admin to merge. Data health lists every organization with no EIN so they are easy to find and fill in later. A malformed EIN is still refused -- blank means we do not hold it, 7412345 means somebody meant to type one and missed.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>The importer reads CSV, not .xlsx. When the sheet is finished: File, then Save As, then choose CSV UTF-8 (Comma delimited). Save only the Awards sheet — Excel will warn that it can save one sheet, which is correct.</t>
+          <t>A blank contact name is fine. Several of these are shared mailboxes with no person behind them, and an email greeting simply reads a little plainer. A blank EMAIL is still refused: a grantee who cannot be reached cannot report.</t>
         </is>
       </c>
     </row>
@@ -673,36 +672,36 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Columns</t>
+          <t>The two things that will break the import</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Dark headers are required — a missing one refuses the whole file. Blue headers are optional; leave any of them blank.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>There is no term_start or term_end column, on purpose</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Report due dates are worked out from an award's term. A 2023 grant would produce a report that is already 600 days overdue, which would show every past grantee as delinquent and could email them chasing letters.</t>
+          <t>1. DATES. Excel rewrites 2023-04-12 as 04/12/2023 when it saves. Every date column in the Awards sheet is already formatted as Text so it will not do that. Do not reformat those columns, and type dates as YYYY-MM-DD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2. EINs. Excel strips a leading zero, so 012345678 becomes 12345678 and the import refuses it. The ein column is also formatted as Text. Dashes are fine either way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>How to save it</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>With no term dates, that cannot happen. Update requests get a due date you choose instead, set when you ask for them.</t>
+          <t>The importer reads CSV, not .xlsx. When the sheet is finished: File, then Save As, then choose CSV UTF-8 (Comma delimited). Save only the Awards sheet — Excel will warn that it can save one sheet, which is correct.</t>
         </is>
       </c>
     </row>
@@ -710,14 +709,14 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>What happens after the import</t>
+          <t>Columns</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1. Publish the report form. 2. Request updates for 2023 to 2025 with a due date. 3. Tell past grantees to go to the tell-us page. 4. Approve each claim, which connects that person to their grant.</t>
+          <t>Dark headers are required — a missing one refuses the whole file. Blue headers are optional; leave any of them blank.</t>
         </is>
       </c>
     </row>
@@ -725,177 +724,214 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>What is left to fill in</t>
+          <t>There is no term_start or term_end column, on purpose</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>The Awards sheet is PRE-FILLED with the thirteen 2025 recipients. The three yellow columns are the ones still to fill in: ein, awarded_date and grantee_contact_name. Everything else is done.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+          <t>Report due dates are worked out from an award's term. A 2023 grant would produce a report that is already 600 days overdue, which would show every past grantee as delinquent and could email them chasing letters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>With no term dates, that cannot happen. Update requests get a due date you choose instead, set when you ask for them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>What happens after the import</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>1. Publish the report form. 2. Request updates for 2023 to 2025 with a due date. 3. Tell past grantees to go to the tell-us page. 4. Approve each claim, which connects that person to their grant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>What is left to fill in</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>The Awards sheet is PRE-FILLED with the thirteen 2025 recipients. ONE yellow column is still to fill in: awarded_date. Put the 2025 announcement date in all thirteen rows. ein and grantee_contact_name are worth adding from your records but the import no longer needs them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>One row per grant, not per organization</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>An organization funded in both 2024 and 2025 gets two rows with the same name and EIN. They are matched on EIN and become one organization with two awards.</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Every column, and what goes in it</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    external_reference  —  Your own unique id for this grant. Any text. Must be unique in the file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    organization_name  —  Legal name of the nonprofit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ein  —  Nine digits. 74-1234567 or 741234567 both fine. TEXT COLUMN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    program_slug  —  Always inspire-change</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    awarded_amount  —  25000 or $25,000 or 25000.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    awarded_date  —  YYYY-MM-DD. TEXT COLUMN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    grantee_contact_name  —  Person who ran the grant.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    grantee_contact_email  —  Where their sign-in link goes. Must be reachable today.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
+          <t xml:space="preserve">    external_reference  —  Your own unique id for this grant. Any text. Must be unique in the file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    organization_name  —  Legal name of the nonprofit.</t>
+        </is>
+      </c>
+    </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    program_slug  —  Always inspire-change</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    fiscal_year  —  2023, 2024 or 2025</t>
+          <t xml:space="preserve">    awarded_amount  —  25000 or $25,000 or 25000.00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    status  —  completed for past grants</t>
+          <t xml:space="preserve">    awarded_date  —  YYYY-MM-DD. TEXT COLUMN.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    grantee_contact_phone  —  Optional.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    notes  —  Anything useful to staff. Never shown to the grantee.</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">    grantee_contact_email  —  Where their sign-in link goes. Must be reachable today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    announcement_date  —  YYYY-MM-DD. Optional.</t>
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    agreement_signed_date  —  YYYY-MM-DD. Optional.</t>
+          <t xml:space="preserve">    ein  —  Nine digits, from their W-9. BLANK IS FINE. TEXT COLUMN.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    w9_received_date  —  YYYY-MM-DD. Optional.</t>
+          <t xml:space="preserve">    grantee_contact_name  —  Person who ran the grant. Blank is fine for a shared mailbox.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    media_release_date  —  YYYY-MM-DD. Optional.</t>
+          <t xml:space="preserve">    fiscal_year  —  2023, 2024 or 2025</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    is_multi_year  —  yes or no. Leave blank for no.</t>
+          <t xml:space="preserve">    status  —  completed for past grants</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    grantee_contact_phone  —  Optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    notes  —  Anything useful to staff. Never shown to the grantee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    announcement_date  —  YYYY-MM-DD. Optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    agreement_signed_date  —  YYYY-MM-DD. Optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    w9_received_date  —  YYYY-MM-DD. Optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    media_release_date  —  YYYY-MM-DD. Optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    is_multi_year  —  yes or no. Leave blank for no.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">    parent_external_reference  —  For a renewal: the external_reference of the first year.</t>
         </is>
@@ -917,12 +953,12 @@
   <cols>
     <col width="26" customWidth="1" style="5" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" style="5" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" style="5" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="29" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" style="5" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" style="5" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="29" customWidth="1" min="11" max="11"/>
@@ -948,32 +984,32 @@
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
+          <t>program_slug</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>awarded_amount</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>awarded_date</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>grantee_contact_email</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
           <t>ein</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>program_slug</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>awarded_amount</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>awarded_date</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>grantee_contact_name</t>
-        </is>
-      </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
-          <t>grantee_contact_email</t>
         </is>
       </c>
       <c r="I1" s="7" t="inlineStr">
@@ -1038,24 +1074,24 @@
           <t>Boys &amp; Girls Club of Brazoria County</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr"/>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>inspire-change</t>
+        </is>
+      </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>inspire-change</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
           <t>25000</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr"/>
-      <c r="G2" s="13" t="inlineStr"/>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr"/>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>anewman@bgcbrazoria.org</t>
         </is>
       </c>
+      <c r="G2" s="10" t="inlineStr"/>
+      <c r="H2" s="11" t="inlineStr"/>
       <c r="I2" s="10" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1083,24 +1119,24 @@
           <t>Career and Recovery Resources, Inc.</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr"/>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>inspire-change</t>
+        </is>
+      </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>inspire-change</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr"/>
-      <c r="G3" s="13" t="inlineStr"/>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr"/>
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>nkechi.agwuenu@careerandrecovery.org</t>
         </is>
       </c>
+      <c r="G3" s="10" t="inlineStr"/>
+      <c r="H3" s="11" t="inlineStr"/>
       <c r="I3" s="10" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1128,24 +1164,24 @@
           <t>Family Scholar House</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr"/>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>inspire-change</t>
+        </is>
+      </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>inspire-change</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
           <t>18000</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr"/>
-      <c r="G4" s="13" t="inlineStr"/>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr"/>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>fshgrants@familyscholarhouse.org</t>
         </is>
       </c>
+      <c r="G4" s="10" t="inlineStr"/>
+      <c r="H4" s="11" t="inlineStr"/>
       <c r="I4" s="10" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1173,24 +1209,24 @@
           <t>Harmony House</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>inspire-change</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>inspire-change</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr"/>
-      <c r="G5" s="13" t="inlineStr"/>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr"/>
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>allison_zapata@harmonyhouse.org</t>
         </is>
       </c>
+      <c r="G5" s="10" t="inlineStr"/>
+      <c r="H5" s="11" t="inlineStr"/>
       <c r="I5" s="10" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1218,24 +1254,24 @@
           <t>Harvest for Hungry</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr"/>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>inspire-change</t>
+        </is>
+      </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>inspire-change</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr"/>
-      <c r="G6" s="13" t="inlineStr"/>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr"/>
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>gluna@harvestforthehungrytexas.org</t>
         </is>
       </c>
+      <c r="G6" s="10" t="inlineStr"/>
+      <c r="H6" s="11" t="inlineStr"/>
       <c r="I6" s="10" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1263,24 +1299,24 @@
           <t>Her Well Center, Inc.</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr"/>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>inspire-change</t>
+        </is>
+      </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>inspire-change</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr"/>
-      <c r="G7" s="13" t="inlineStr"/>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr"/>
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>creyes@herwell.org</t>
         </is>
       </c>
+      <c r="G7" s="10" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr"/>
       <c r="I7" s="10" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1308,24 +1344,24 @@
           <t>HYPE Freedom School</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr"/>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>inspire-change</t>
+        </is>
+      </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>inspire-change</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr"/>
-      <c r="G8" s="13" t="inlineStr"/>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr"/>
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>brandi@hypefs.org</t>
         </is>
       </c>
+      <c r="G8" s="10" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr"/>
       <c r="I8" s="10" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1353,24 +1389,24 @@
           <t>Prison Entrepreneurship Program (PEP)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>inspire-change</t>
+        </is>
+      </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>inspire-change</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr"/>
-      <c r="G9" s="13" t="inlineStr"/>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr"/>
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>mriley@pep.org</t>
         </is>
       </c>
+      <c r="G9" s="10" t="inlineStr"/>
+      <c r="H9" s="11" t="inlineStr"/>
       <c r="I9" s="10" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1398,24 +1434,24 @@
           <t>Stay Tuned for the Arts</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>inspire-change</t>
+        </is>
+      </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>inspire-change</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
           <t>15000</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr"/>
-      <c r="G10" s="13" t="inlineStr"/>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr"/>
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>donate@staytunedforvets.org</t>
         </is>
       </c>
+      <c r="G10" s="10" t="inlineStr"/>
+      <c r="H10" s="11" t="inlineStr"/>
       <c r="I10" s="10" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1443,24 +1479,24 @@
           <t>Target Hunger</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>inspire-change</t>
+        </is>
+      </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>inspire-change</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr"/>
-      <c r="G11" s="13" t="inlineStr"/>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr"/>
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>hannah@targethunger.org</t>
         </is>
       </c>
+      <c r="G11" s="10" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr"/>
       <c r="I11" s="10" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1488,24 +1524,24 @@
           <t>The Arc of Katy</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr"/>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>inspire-change</t>
+        </is>
+      </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>inspire-change</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
           <t>12000</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr"/>
-      <c r="G12" s="13" t="inlineStr"/>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr"/>
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>saugust@thearcofkaty.org</t>
         </is>
       </c>
+      <c r="G12" s="10" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr"/>
       <c r="I12" s="10" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1533,24 +1569,24 @@
           <t>US Dream Academy</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr"/>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>inspire-change</t>
+        </is>
+      </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>inspire-change</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr"/>
-      <c r="G13" s="13" t="inlineStr"/>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr"/>
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>whull@usdreamacademy.org</t>
         </is>
       </c>
+      <c r="G13" s="10" t="inlineStr"/>
+      <c r="H13" s="11" t="inlineStr"/>
       <c r="I13" s="10" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1578,24 +1614,24 @@
           <t>Youth Development Center</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr"/>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>inspire-change</t>
+        </is>
+      </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>inspire-change</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
           <t>29000</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr"/>
-      <c r="G14" s="13" t="inlineStr"/>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>bhuff@ydc.org</t>
         </is>
       </c>
+      <c r="G14" s="10" t="inlineStr"/>
+      <c r="H14" s="11" t="inlineStr"/>
       <c r="I14" s="10" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1614,7 +1650,7 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="D2:D400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"inspire-change"</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/docs/inspire-change-2025-grants.xlsx
+++ b/docs/inspire-change-2025-grants.xlsx
@@ -631,7 +631,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -646,7 +645,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -668,7 +666,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -690,7 +687,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
@@ -705,7 +701,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
@@ -720,7 +715,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
@@ -742,7 +736,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
@@ -757,7 +750,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
@@ -772,7 +764,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
@@ -787,7 +778,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
@@ -795,7 +785,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
@@ -845,7 +834,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
@@ -1084,7 +1072,11 @@
           <t>25000</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr"/>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
       <c r="F2" s="11" t="inlineStr">
         <is>
           <t>anewman@bgcbrazoria.org</t>
@@ -1129,7 +1121,11 @@
           <t>50000</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr"/>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
           <t>nkechi.agwuenu@careerandrecovery.org</t>
@@ -1174,7 +1170,11 @@
           <t>18000</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr"/>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
           <t>fshgrants@familyscholarhouse.org</t>
@@ -1219,7 +1219,11 @@
           <t>50000</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr"/>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
           <t>allison_zapata@harmonyhouse.org</t>
@@ -1264,7 +1268,11 @@
           <t>50000</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr"/>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
           <t>gluna@harvestforthehungrytexas.org</t>
@@ -1309,7 +1317,11 @@
           <t>50000</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr"/>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
           <t>creyes@herwell.org</t>
@@ -1354,7 +1366,11 @@
           <t>50000</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr"/>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
           <t>brandi@hypefs.org</t>
@@ -1399,7 +1415,11 @@
           <t>40000</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr"/>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
           <t>mriley@pep.org</t>
@@ -1444,7 +1464,11 @@
           <t>15000</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr"/>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
           <t>donate@staytunedforvets.org</t>
@@ -1489,7 +1513,11 @@
           <t>30000</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr"/>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
           <t>hannah@targethunger.org</t>
@@ -1534,7 +1562,11 @@
           <t>12000</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr"/>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
           <t>saugust@thearcofkaty.org</t>
@@ -1579,7 +1611,11 @@
           <t>50000</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr"/>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
           <t>whull@usdreamacademy.org</t>
@@ -1624,7 +1660,11 @@
           <t>29000</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr"/>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
           <t>bhuff@ydc.org</t>
